--- a/public/exports/29188475.xlsx
+++ b/public/exports/29188475.xlsx
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493619</t>
+          <t xml:space="preserve">2495761</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F5">
-        <v>1592</v>
+        <v>1364</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494366</t>
+          <t xml:space="preserve">2495761</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -290,7 +290,7 @@
         </is>
       </c>
       <c r="F6">
-        <v>973</v>
+        <v>624</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494366</t>
+          <t xml:space="preserve">2501202</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F7">
-        <v>1300</v>
+        <v>1181</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2495761</t>
+          <t xml:space="preserve">2586303</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F8">
-        <v>1364</v>
+        <v>332</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2495761</t>
+          <t xml:space="preserve">272693</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>624</v>
+        <v>1297</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2501202</t>
+          <t xml:space="preserve">272693</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F10">
-        <v>1181</v>
+        <v>574</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2586303</t>
+          <t xml:space="preserve">272693</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F11">
-        <v>332</v>
+        <v>1037</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">719853, 2580339</t>
+          <t xml:space="preserve">272693, 272694</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F12">
-        <v>369</v>
+        <v>1229</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">719853, 2580339</t>
+          <t xml:space="preserve">272695</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F13">
-        <v>516</v>
+        <v>333</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">719853, 2580339</t>
+          <t xml:space="preserve">273579, 273581</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F14">
-        <v>251</v>
+        <v>1765</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">719857, 8970913</t>
+          <t xml:space="preserve">273580</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F15">
-        <v>352</v>
+        <v>404</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">719919, 2583548</t>
+          <t xml:space="preserve">278068, 278069</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>938</v>
+        <v>3518</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">719935, 8970979</t>
+          <t xml:space="preserve">719853, 2580339</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F17">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">7781615</t>
+          <t xml:space="preserve">719853, 2580339</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F18">
-        <v>1739</v>
+        <v>516</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,35 +931,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494663</t>
+          <t xml:space="preserve">719853, 2580339</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F19">
-        <v>695</v>
+        <v>251</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502366</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">8970979</t>
+          <t xml:space="preserve">719857, 8970913</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -990,26 +990,26 @@
         </is>
       </c>
       <c r="F20">
-        <v>1457</v>
+        <v>352</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502367</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1031,35 +1031,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8970979</t>
+          <t xml:space="preserve">719919, 2583548</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F21">
-        <v>826</v>
+        <v>938</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502367</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1081,35 +1081,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">8970979</t>
+          <t xml:space="preserve">719935, 8970979</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F22">
-        <v>1176</v>
+        <v>374</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502367</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1131,35 +1131,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">8970979</t>
+          <t xml:space="preserve">7781615</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F23">
-        <v>1991</v>
+        <v>1739</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502367</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1181,20 +1181,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">8970979</t>
+          <t xml:space="preserve">2494663</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F24">
-        <v>965</v>
+        <v>695</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502367</t>
+          <t xml:space="preserve">311502366</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325124</t>
+          <t xml:space="preserve">8970979</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>1690</v>
+        <v>1457</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507976</t>
+          <t xml:space="preserve">311502367</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1281,25 +1281,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325124</t>
+          <t xml:space="preserve">8970979</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F26">
-        <v>4602</v>
+        <v>826</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507976</t>
+          <t xml:space="preserve">311502367</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1331,25 +1331,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325124</t>
+          <t xml:space="preserve">8970979</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F27">
-        <v>2344</v>
+        <v>1176</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507977</t>
+          <t xml:space="preserve">311502367</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1381,25 +1381,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325124</t>
+          <t xml:space="preserve">8970979</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F28">
-        <v>1918</v>
+        <v>1991</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507976</t>
+          <t xml:space="preserve">311502367</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1431,25 +1431,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580447</t>
+          <t xml:space="preserve">8970979</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F29">
-        <v>2421</v>
+        <v>965</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507982</t>
+          <t xml:space="preserve">311502367</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1481,20 +1481,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580447</t>
+          <t xml:space="preserve">1325124</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F30">
-        <v>1417</v>
+        <v>1690</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507984</t>
+          <t xml:space="preserve">311507976</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1531,20 +1531,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580447</t>
+          <t xml:space="preserve">1325124</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F31">
-        <v>1641</v>
+        <v>4602</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507986</t>
+          <t xml:space="preserve">311507976</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1581,20 +1581,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580447</t>
+          <t xml:space="preserve">1325124</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F32">
-        <v>2100</v>
+        <v>2344</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507980</t>
+          <t xml:space="preserve">311507977</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580447</t>
+          <t xml:space="preserve">1325124</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1640,11 +1640,11 @@
         </is>
       </c>
       <c r="F33">
-        <v>676</v>
+        <v>1918</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507981</t>
+          <t xml:space="preserve">311507976</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493619</t>
+          <t xml:space="preserve">2580447</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1690,16 +1690,16 @@
         </is>
       </c>
       <c r="F34">
-        <v>1736</v>
+        <v>2421</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513872</t>
+          <t xml:space="preserve">311507982</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-20</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1731,25 +1731,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493619</t>
+          <t xml:space="preserve">2580447</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F35">
-        <v>1541</v>
+        <v>1417</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513878</t>
+          <t xml:space="preserve">311507984</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-20</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1781,25 +1781,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493619</t>
+          <t xml:space="preserve">2580447</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F36">
-        <v>9606</v>
+        <v>1641</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513873</t>
+          <t xml:space="preserve">311507986</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-20</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1831,25 +1831,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491982</t>
+          <t xml:space="preserve">2580447</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F37">
-        <v>977</v>
+        <v>2100</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514701</t>
+          <t xml:space="preserve">311507980</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-23</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1881,25 +1881,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491982</t>
+          <t xml:space="preserve">2580447</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F38">
-        <v>1464</v>
+        <v>676</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514701</t>
+          <t xml:space="preserve">311507981</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-23</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491982</t>
+          <t xml:space="preserve">2493619</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39">
-        <v>1140</v>
+        <v>1736</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514701</t>
+          <t xml:space="preserve">311513872</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-23</t>
+          <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1981,25 +1981,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491982</t>
+          <t xml:space="preserve">2493619</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F40">
-        <v>275</v>
+        <v>1541</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514701</t>
+          <t xml:space="preserve">311513876</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-23</t>
+          <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2496094</t>
+          <t xml:space="preserve">2493619</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F41">
-        <v>7175</v>
+        <v>9606</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519033</t>
+          <t xml:space="preserve">311513873</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-10</t>
+          <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585399</t>
+          <t xml:space="preserve">2493619</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F42">
-        <v>494</v>
+        <v>1592</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520451</t>
+          <t xml:space="preserve">311513876</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585399</t>
+          <t xml:space="preserve">2491982</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F43">
-        <v>1627</v>
+        <v>977</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520451</t>
+          <t xml:space="preserve">311514701</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585399</t>
+          <t xml:space="preserve">2491982</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F44">
-        <v>1299</v>
+        <v>1464</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520451</t>
+          <t xml:space="preserve">311514701</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585399</t>
+          <t xml:space="preserve">2491982</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="F45">
-        <v>1958</v>
+        <v>1140</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520448</t>
+          <t xml:space="preserve">311514701</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585399</t>
+          <t xml:space="preserve">2491982</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="F46">
-        <v>1789</v>
+        <v>275</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520451</t>
+          <t xml:space="preserve">311514701</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585399</t>
+          <t xml:space="preserve">2496094</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47">
-        <v>1124</v>
+        <v>7175</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520449</t>
+          <t xml:space="preserve">311519033</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-05-10</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2581322</t>
+          <t xml:space="preserve">2585399</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="F48">
-        <v>647</v>
+        <v>494</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522394</t>
+          <t xml:space="preserve">311520451</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2581322</t>
+          <t xml:space="preserve">2585399</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2440,16 +2440,16 @@
         </is>
       </c>
       <c r="F49">
-        <v>486</v>
+        <v>1627</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522394</t>
+          <t xml:space="preserve">311520451</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2581322</t>
+          <t xml:space="preserve">2585399</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F50">
-        <v>299</v>
+        <v>1299</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522394</t>
+          <t xml:space="preserve">311520451</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,25 +2531,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492828</t>
+          <t xml:space="preserve">2585399</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F51">
-        <v>11412</v>
+        <v>1958</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525403</t>
+          <t xml:space="preserve">311520448</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-04</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492828</t>
+          <t xml:space="preserve">2585399</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F52">
-        <v>764</v>
+        <v>1789</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525403</t>
+          <t xml:space="preserve">311520451</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-04</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499032</t>
+          <t xml:space="preserve">2585399</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F53">
-        <v>1058</v>
+        <v>1124</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526266</t>
+          <t xml:space="preserve">311520449</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499032</t>
+          <t xml:space="preserve">2581322</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F54">
-        <v>745</v>
+        <v>647</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526270</t>
+          <t xml:space="preserve">311522394</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499032</t>
+          <t xml:space="preserve">2581322</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F55">
-        <v>296</v>
+        <v>486</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526267</t>
+          <t xml:space="preserve">311522394</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499032</t>
+          <t xml:space="preserve">2581322</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2790,16 +2790,16 @@
         </is>
       </c>
       <c r="F56">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526268</t>
+          <t xml:space="preserve">311522394</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499032</t>
+          <t xml:space="preserve">2492828</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F57">
-        <v>519</v>
+        <v>11412</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526271</t>
+          <t xml:space="preserve">311525401</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8141300</t>
+          <t xml:space="preserve">2492828</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F58">
-        <v>1564</v>
+        <v>764</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531956</t>
+          <t xml:space="preserve">311525401</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-29</t>
+          <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">8141300</t>
+          <t xml:space="preserve">2499032</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F59">
-        <v>325</v>
+        <v>1058</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531956</t>
+          <t xml:space="preserve">311526266</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-29</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">8141300</t>
+          <t xml:space="preserve">2499032</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F60">
-        <v>2032</v>
+        <v>745</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531956</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-29</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,25 +3031,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494640</t>
+          <t xml:space="preserve">2499032</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F61">
-        <v>675</v>
+        <v>296</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532866</t>
+          <t xml:space="preserve">311526267</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-01</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494640</t>
+          <t xml:space="preserve">2499032</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F62">
-        <v>675</v>
+        <v>285</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532866</t>
+          <t xml:space="preserve">311526268</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-01</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492876</t>
+          <t xml:space="preserve">2499032</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F63">
-        <v>2115</v>
+        <v>519</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533132</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9769474</t>
+          <t xml:space="preserve">8141300</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F64">
-        <v>746</v>
+        <v>1564</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533569</t>
+          <t xml:space="preserve">311531956</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-06-29</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9769474</t>
+          <t xml:space="preserve">8141300</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F65">
-        <v>679</v>
+        <v>325</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533839</t>
+          <t xml:space="preserve">311531956</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-06</t>
+          <t xml:space="preserve">2031-06-29</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9769474</t>
+          <t xml:space="preserve">8141300</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F66">
-        <v>679</v>
+        <v>2032</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533838</t>
+          <t xml:space="preserve">311531956</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-06</t>
+          <t xml:space="preserve">2031-06-29</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">100080165</t>
+          <t xml:space="preserve">2494640</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="F67">
-        <v>2431</v>
+        <v>675</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534182</t>
+          <t xml:space="preserve">311532866</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2587199</t>
+          <t xml:space="preserve">2494640</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F68">
-        <v>2134</v>
+        <v>675</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534181</t>
+          <t xml:space="preserve">311532866</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,25 +3431,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2495761</t>
+          <t xml:space="preserve">2492876</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F69">
-        <v>394</v>
+        <v>2115</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534554</t>
+          <t xml:space="preserve">311533132</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-08</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579156</t>
+          <t xml:space="preserve">9769474</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F70">
-        <v>936</v>
+        <v>746</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534563</t>
+          <t xml:space="preserve">311533569</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-08</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580442</t>
+          <t xml:space="preserve">9769474</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3540,16 +3540,16 @@
         </is>
       </c>
       <c r="F71">
-        <v>1250</v>
+        <v>679</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534561</t>
+          <t xml:space="preserve">311533839</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-08</t>
+          <t xml:space="preserve">2031-07-06</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">272693</t>
+          <t xml:space="preserve">9769474</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F72">
-        <v>1297</v>
+        <v>679</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564100</t>
+          <t xml:space="preserve">311533838</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-08</t>
+          <t xml:space="preserve">2031-07-06</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">272693</t>
+          <t xml:space="preserve">100080165</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F73">
-        <v>574</v>
+        <v>2431</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564102</t>
+          <t xml:space="preserve">311534182</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-08</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">272693</t>
+          <t xml:space="preserve">2587199</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>1037</v>
+        <v>2134</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564104</t>
+          <t xml:space="preserve">311534181</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-08</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,20 +3731,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">272693, 272694</t>
+          <t xml:space="preserve">2495761</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F75">
-        <v>1229</v>
+        <v>394</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564103</t>
+          <t xml:space="preserve">311534554</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3781,20 +3781,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">272695</t>
+          <t xml:space="preserve">2579156</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F76">
-        <v>333</v>
+        <v>936</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564101</t>
+          <t xml:space="preserve">311534563</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">273579, 273581</t>
+          <t xml:space="preserve">2580442</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3840,11 +3840,11 @@
         </is>
       </c>
       <c r="F77">
-        <v>1765</v>
+        <v>1250</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534458</t>
+          <t xml:space="preserve">311534561</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4386,15 +4386,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F88">
-        <v>416</v>
+        <v>973</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539269</t>
+          <t xml:space="preserve">311539272</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4436,15 +4436,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F89">
-        <v>1387</v>
+        <v>1300</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539175</t>
+          <t xml:space="preserve">311539272</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">7781615</t>
+          <t xml:space="preserve">2494366</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F90">
-        <v>1119</v>
+        <v>416</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541554</t>
+          <t xml:space="preserve">311539269</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-18</t>
+          <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,25 +4531,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7781615</t>
+          <t xml:space="preserve">2494366</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F91">
-        <v>633</v>
+        <v>1387</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541554</t>
+          <t xml:space="preserve">311539175</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-18</t>
+          <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,20 +4581,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7781616</t>
+          <t xml:space="preserve">7781615</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F92">
-        <v>2900</v>
+        <v>1119</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541553</t>
+          <t xml:space="preserve">311541554</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">273580</t>
+          <t xml:space="preserve">7781615</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F93">
-        <v>404</v>
+        <v>633</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542625</t>
+          <t xml:space="preserve">311541554</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-23</t>
+          <t xml:space="preserve">2031-08-18</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2496094</t>
+          <t xml:space="preserve">7781616</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F94">
-        <v>698</v>
+        <v>2900</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543099</t>
+          <t xml:space="preserve">311541553</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-25</t>
+          <t xml:space="preserve">2031-08-18</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,20 +4731,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580360</t>
+          <t xml:space="preserve">2496094</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F95">
-        <v>581</v>
+        <v>698</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543100</t>
+          <t xml:space="preserve">311543099</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4781,20 +4781,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580362</t>
+          <t xml:space="preserve">2580360</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F96">
-        <v>379</v>
+        <v>581</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543101</t>
+          <t xml:space="preserve">311543100</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585634</t>
+          <t xml:space="preserve">2580362</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F97">
-        <v>833</v>
+        <v>379</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543427</t>
+          <t xml:space="preserve">311543101</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-26</t>
+          <t xml:space="preserve">2031-08-25</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499489</t>
+          <t xml:space="preserve">2585634</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4890,16 +4890,16 @@
         </is>
       </c>
       <c r="F98">
-        <v>2089</v>
+        <v>833</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544512</t>
+          <t xml:space="preserve">311543427</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4936,15 +4936,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F99">
-        <v>253</v>
+        <v>2089</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544514</t>
+          <t xml:space="preserve">311544511</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4981,20 +4981,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827159</t>
+          <t xml:space="preserve">2499489</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F100">
-        <v>707</v>
+        <v>253</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544498</t>
+          <t xml:space="preserve">311544511</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493974</t>
+          <t xml:space="preserve">9827159</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5040,16 +5040,16 @@
         </is>
       </c>
       <c r="F101">
-        <v>368</v>
+        <v>707</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544973</t>
+          <t xml:space="preserve">311544498</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-01</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,20 +5081,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499035</t>
+          <t xml:space="preserve">2493974</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F102">
-        <v>642</v>
+        <v>368</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544971</t>
+          <t xml:space="preserve">311544973</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8975253</t>
+          <t xml:space="preserve">2499035</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F103">
-        <v>585</v>
+        <v>642</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545558</t>
+          <t xml:space="preserve">311544971</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-03</t>
+          <t xml:space="preserve">2031-09-01</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8295199</t>
+          <t xml:space="preserve">8975253</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5190,16 +5190,16 @@
         </is>
       </c>
       <c r="F104">
-        <v>715</v>
+        <v>585</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545939</t>
+          <t xml:space="preserve">311545558</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-06</t>
+          <t xml:space="preserve">2031-09-03</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">100281363</t>
+          <t xml:space="preserve">8295199</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="F105">
-        <v>433</v>
+        <v>715</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546918</t>
+          <t xml:space="preserve">311545939</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-06</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7941733</t>
+          <t xml:space="preserve">100281363</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5290,11 +5290,11 @@
         </is>
       </c>
       <c r="F106">
-        <v>538</v>
+        <v>433</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546917</t>
+          <t xml:space="preserve">311546918</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9945281</t>
+          <t xml:space="preserve">7941733</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5340,16 +5340,16 @@
         </is>
       </c>
       <c r="F107">
-        <v>300</v>
+        <v>538</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548105</t>
+          <t xml:space="preserve">311546917</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-14</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491982</t>
+          <t xml:space="preserve">9945281</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F108">
-        <v>365</v>
+        <v>300</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548233</t>
+          <t xml:space="preserve">311548105</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-15</t>
+          <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,20 +5431,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493365</t>
+          <t xml:space="preserve">2491982</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F109">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548273</t>
+          <t xml:space="preserve">311548233</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2495779</t>
+          <t xml:space="preserve">2493365</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5490,11 +5490,11 @@
         </is>
       </c>
       <c r="F110">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548277</t>
+          <t xml:space="preserve">311548273</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9340703</t>
+          <t xml:space="preserve">2495779</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5540,11 +5540,11 @@
         </is>
       </c>
       <c r="F111">
-        <v>496</v>
+        <v>381</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548275</t>
+          <t xml:space="preserve">311548277</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2588105</t>
+          <t xml:space="preserve">9340703</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="F112">
-        <v>535</v>
+        <v>496</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548921</t>
+          <t xml:space="preserve">311548275</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-17</t>
+          <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492872</t>
+          <t xml:space="preserve">2588105</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5640,16 +5640,16 @@
         </is>
       </c>
       <c r="F113">
-        <v>352</v>
+        <v>535</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550934</t>
+          <t xml:space="preserve">311548921</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-09-17</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F114">
@@ -5736,11 +5736,11 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F115">
-        <v>406</v>
+        <v>352</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8127744</t>
+          <t xml:space="preserve">2492872</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F116">
-        <v>697</v>
+        <v>406</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551270</t>
+          <t xml:space="preserve">311550934</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-28</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579410</t>
+          <t xml:space="preserve">8127744</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F117">
-        <v>2332</v>
+        <v>697</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557163</t>
+          <t xml:space="preserve">311551269</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-25</t>
+          <t xml:space="preserve">2031-09-28</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">100031923</t>
+          <t xml:space="preserve">2579410</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5890,16 +5890,16 @@
         </is>
       </c>
       <c r="F118">
-        <v>1359</v>
+        <v>2332</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557852</t>
+          <t xml:space="preserve">311557163</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-27</t>
+          <t xml:space="preserve">2031-10-25</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,20 +5931,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">100328633</t>
+          <t xml:space="preserve">100031923</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F119">
-        <v>283</v>
+        <v>1359</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557973</t>
+          <t xml:space="preserve">311557852</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2581015</t>
+          <t xml:space="preserve">100328633</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F120">
-        <v>369</v>
+        <v>283</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558145</t>
+          <t xml:space="preserve">311557973</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2031-10-27</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562931</t>
+          <t xml:space="preserve">311562929</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562920</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562924</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562926</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562919</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8970979</t>
+          <t xml:space="preserve">2581015</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F132">
-        <v>1672</v>
+        <v>369</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585557</t>
+          <t xml:space="preserve">311567228</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-16</t>
+          <t xml:space="preserve">2031-12-10</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585458</t>
+          <t xml:space="preserve">8970979</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F133">
-        <v>1441</v>
+        <v>1672</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624091</t>
+          <t xml:space="preserve">311585557</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-30</t>
+          <t xml:space="preserve">2032-03-16</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">278068, 278069</t>
+          <t xml:space="preserve">2585458</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6690,16 +6690,16 @@
         </is>
       </c>
       <c r="F134">
-        <v>3518</v>
+        <v>1441</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682804</t>
+          <t xml:space="preserve">311624091</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-24</t>
+          <t xml:space="preserve">2032-08-30</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">

--- a/public/exports/29188475.xlsx
+++ b/public/exports/29188475.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J134"/>
+  <dimension ref="A1:L134"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 12A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100075735</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>851</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 12B</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">100075735</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>463</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vesterled 24</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">100075735</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>976</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bækvej 3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2495761</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>1364</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bækvej 3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2495761</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>624</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Førslev Skolevej 9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">2501202</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>1181</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevangen 8A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4683</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">2586303</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>332</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frederiksgade 8A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">272693</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>1297</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frederiksgade 44</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">272693</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>574</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frederiksgade 10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">272693</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>1037</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frederiksgade 8E</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">272693, 272694</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>1229</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frederiksgade 8D</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">272695</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>333</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grøndalsvej 8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">273579, 273581</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>1765</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sygehusvej 5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">273580</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>404</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindevej 13B</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">278068, 278069</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>3518</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østervej 4</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">719853, 2580339</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>369</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østervej 4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">719853, 2580339</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>516</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østervej 4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">719853, 2580339</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>251</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jesper Olsens Vej 6</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">719857, 8970913</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>352</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnevej 10</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4654</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">719919, 2583548</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>938</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dannebrogsvej 3</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4654</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">719935, 8970979</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>374</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bavnestræde 28</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">7781615</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>1739</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grøndalsvej 35</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2494663</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>695</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311502366</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dannebrogsvej 1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4654</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">8970979</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>1457</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311502367</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dannebrogsvej 1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4654</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">8970979</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>826</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311502367</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dannebrogsvej 1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4654</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">8970979</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>1176</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311502367</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dannebrogsvej 1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4654</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">8970979</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>1991</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311502367</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dannebrogsvej 1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4654</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">8970979</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>965</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311502367</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Eskilstrupvej 3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4683</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">1325124</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>1690</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311507976</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Eskilstrupvej 3</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4683</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">1325124</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>4602</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311507976</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Eskilstrupvej 7</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4683</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">1325124</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>2344</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311507977</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Eskilstrupvej 3</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4683</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">1325124</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>1918</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311507976</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl Strandvej 12</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580447</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>2421</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311507982</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl Strandvej 12</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580447</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>1417</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311507984</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl Strandvej 12</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580447</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>1641</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311507986</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl Strandvej 12</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580447</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>2100</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311507980</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl Strandvej 12</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580447</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>676</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311507981</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bækvej 14</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2493619</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>1736</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311513872</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bækvej 14</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2493619</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>1541</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311513876</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bækvej 14</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2493619</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>9606</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311513873</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bækvej 14</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2493619</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>1592</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311513876</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frederiksgade 9</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2491982</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>977</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311514701</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frederiksgade 9</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2491982</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>1464</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311514701</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frederiksgade 9</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2491982</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>1140</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311514701</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frederiksgade 9</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2491982</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>275</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311514701</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vibeeng Alle 2</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2496094</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>7175</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311519033</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-10</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 39</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2585399</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>494</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311520451</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 39</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4653</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2585399</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>1627</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311520451</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 39</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4653</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2585399</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>1299</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311520451</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevej 6A</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4653</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2585399</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>1958</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311520448</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 39</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4653</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2585399</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>1789</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311520451</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 39</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4653</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2585399</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>1124</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311520449</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industriparken 4</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2581322</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>647</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311522394</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industriparken 4</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2581322</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>486</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311522394</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industriparken 4</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2581322</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>299</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311522394</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sofiendalsvej 42A</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2492828</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>11412</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311525401</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sofiendalsvej 42A</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2492828</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>764</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311525401</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Terslev Skolevej 34A</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2499032</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>1058</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311526266</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Terslev Skolevej 34A</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2499032</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>745</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311526269</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Terslev Skolevej 34B</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2499032</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>296</v>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311526267</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311526269</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Terslev Skolevej 34A</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2499032</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>285</v>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311526268</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311526269</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Terslev Skolevej 36</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2499032</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>519</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311526269</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingvej 7</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">8141300</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>1564</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311531956</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-29</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingvej 7</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">8141300</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>325</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311531956</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-29</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingvej 7</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">8141300</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>2032</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311531956</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-29</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grøndalsvej 29A</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2494640</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>675</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311532866</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grøndalsvej 31A</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2494640</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>675</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311532866</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sofiendalsvej 42C</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2492876</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>2115</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311533132</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thujavej 19</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4683</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">9769474</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>746</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311533569</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thujavej 1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4683</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">9769474</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>679</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311533839</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-06</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thujavej 10</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4683</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">9769474</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>679</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311533838</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-06</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 14</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">100080165</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>2431</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311534182</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevej 68A</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4683</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2587199</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>2134</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311534181</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bækvej 3</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2495761</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>394</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311534554</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Heeringvej 3</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2579156</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>936</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311534563</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusvej 4</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580442</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>1250</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311534561</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevangen 8</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4683</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">7968886</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>946</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311534555</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grøndalsvej 25A</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">8780170</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>660</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311534676</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grøndalsvej 27A</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">8780170</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>660</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311534676</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grøndalsvej 33A</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">8780170</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>660</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311534676</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jernbanegade 62</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2492101</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>4270</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311554854</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-19</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Postvej 6</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4654</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">8135543</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>1376</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311536815</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-19</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bavnestræde 48</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2579174</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>1503</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311537312</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-22</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bavnestræde 46</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2579174</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>1088</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311537312</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-22</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bavnestræde 42</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2579174</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>351</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311537312</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-07-22</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstøvej 86</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2581990</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>4123</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311538599</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-02</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 12E</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2494366</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>973</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">311539272</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 12</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2494366</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>1300</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">311539272</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4481,33 +5371,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 12C</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2494366</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>416</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">311539269</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4531,33 +5431,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 12G</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2494366</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="H91">
         <v>1387</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">311539175</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4581,33 +5491,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bavnestræde 28</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">7781615</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>1119</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">311541554</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-18</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4631,33 +5551,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bavnestræde 28</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">7781615</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="H93">
         <v>633</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">311541554</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-18</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4681,33 +5611,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bavnestræde 36</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">7781616</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="H94">
         <v>2900</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">311541553</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-18</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4731,33 +5671,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndermarken 1</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2496094</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="H95">
         <v>698</v>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">311543099</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-25</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4781,33 +5731,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl Strandvej 2</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580360</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="H96">
         <v>581</v>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">311543100</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-25</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4831,33 +5791,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl Strandvej 2</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580362</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>379</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">311543101</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-25</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4881,33 +5851,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 42</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4653</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2585634</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F98">
+      <c r="H98">
         <v>833</v>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">311543427</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4931,33 +5911,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 18A</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2499489</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F99">
+      <c r="H99">
         <v>2089</v>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311544511</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311544512</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4981,33 +5971,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 18C</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2499489</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F100">
+      <c r="H100">
         <v>253</v>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311544511</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
+      <c r="I100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311544514</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5031,33 +6031,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ny Strandvej 3A</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t xml:space="preserve">9827159</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>707</v>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">311544498</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5081,33 +6091,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Maglemosevej 9</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2493974</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F102">
+      <c r="H102">
         <v>368</v>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">311544973</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-01</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5131,33 +6151,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Terslev Skolevej 30B</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2499035</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F103">
+      <c r="H103">
         <v>642</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">311544971</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-01</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5181,33 +6211,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drosselvej 1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4683</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">8975253</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>585</v>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">311545558</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-03</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5231,33 +6271,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstøvej 3</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">8295199</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F105">
+      <c r="H105">
         <v>715</v>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">311545939</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-06</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5281,33 +6331,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstøvej 11A</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t xml:space="preserve">100281363</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F106">
+      <c r="H106">
         <v>433</v>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">311546918</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5331,33 +6391,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindeparken 33</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t xml:space="preserve">7941733</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F107">
+      <c r="H107">
         <v>538</v>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">311546917</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
+      <c r="K107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5381,33 +6451,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 8</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t xml:space="preserve">9945281</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F108">
+      <c r="H108">
         <v>300</v>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t xml:space="preserve">311548105</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
+      <c r="K108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5431,33 +6511,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstevænget 23</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2491982</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>365</v>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t xml:space="preserve">311548233</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
+      <c r="K109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5481,33 +6571,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sofiendalsvej 4</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2493365</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>374</v>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t xml:space="preserve">311548273</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
+      <c r="K110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5531,33 +6631,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Valmuevej 2</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2495779</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F111">
+      <c r="H111">
         <v>381</v>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t xml:space="preserve">311548277</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
+      <c r="K111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5581,33 +6691,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 10</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t xml:space="preserve">9340703</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F112">
+      <c r="H112">
         <v>496</v>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t xml:space="preserve">311548275</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
+      <c r="K112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5631,33 +6751,43 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vindbyholtvej 30B</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2588105</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F113">
+      <c r="H113">
         <v>535</v>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t xml:space="preserve">311548921</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-17</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
+      <c r="K113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5681,33 +6811,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frøgårdsvej 21</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2492872</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F114">
+      <c r="H114">
         <v>352</v>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t xml:space="preserve">311550934</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5731,33 +6871,43 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frøgårdsvej 21</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2492872</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F115">
+      <c r="H115">
         <v>352</v>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t xml:space="preserve">311550934</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
+      <c r="K115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5781,33 +6931,43 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frøgårdsvej 21</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2492872</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F116">
+      <c r="H116">
         <v>406</v>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t xml:space="preserve">311550934</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
+      <c r="K116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5831,33 +6991,43 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Førslev Bygade 16A</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t xml:space="preserve">8127744</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F117">
+      <c r="H117">
         <v>697</v>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311551269</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
+      <c r="I117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311551270</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-28</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
+      <c r="K117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5881,33 +7051,43 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindhardsvej 5</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4690</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2579410</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>2332</v>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t xml:space="preserve">311557163</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-25</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
+      <c r="K118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5931,33 +7111,43 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østervej 2A</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t xml:space="preserve">100031923</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>1359</v>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t xml:space="preserve">311557852</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-27</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
+      <c r="K119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5981,33 +7171,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ny Strandvej 1C</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t xml:space="preserve">100328633</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F120">
+      <c r="H120">
         <v>283</v>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t xml:space="preserve">311557973</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-27</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
+      <c r="K120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6031,33 +7231,43 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hertelsvej 18</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t xml:space="preserve">9978417</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F121">
+      <c r="H121">
         <v>1430</v>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t xml:space="preserve">311560035</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-05</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
+      <c r="K121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6081,33 +7291,43 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hertelsvej 16</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580961</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F122">
+      <c r="H122">
         <v>288</v>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t xml:space="preserve">311562929</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="J122" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
+      <c r="K122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6131,33 +7351,43 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstøvej 78A</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580963</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F123">
+      <c r="H123">
         <v>2118</v>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="I123" t="inlineStr">
         <is>
           <t xml:space="preserve">311562912</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="J123" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
+      <c r="K123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6181,33 +7411,43 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstøvej 78A</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580963</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F124">
+      <c r="H124">
         <v>1875</v>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t xml:space="preserve">311562918</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="J124" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
+      <c r="K124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6231,33 +7471,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstøvej 78B</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580963</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="F125">
+      <c r="H125">
         <v>1266</v>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t xml:space="preserve">311562918</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="J125" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
+      <c r="K125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6281,33 +7531,43 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstøvej 78A</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580963</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F126">
+      <c r="H126">
         <v>2727</v>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t xml:space="preserve">311562913</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="J126" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
+      <c r="K126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6331,33 +7591,43 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstøvej 78A</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580963</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>2961</v>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311562914</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
+      <c r="I127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311562918</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
+      <c r="K127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6381,33 +7651,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstøvej 78A</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580963</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F128">
+      <c r="H128">
         <v>2156</v>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="I128" t="inlineStr">
         <is>
           <t xml:space="preserve">311562915</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="J128" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
+      <c r="K128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6431,33 +7711,43 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstøvej 78A</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580963</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F129">
+      <c r="H129">
         <v>516</v>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t xml:space="preserve">311562916</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
+      <c r="K129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6481,33 +7771,43 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstøvej 78A</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580963</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F130">
+      <c r="H130">
         <v>890</v>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t xml:space="preserve">311562918</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="J130" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
+      <c r="K130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6531,33 +7831,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstøvej 78A</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2580963</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F131">
+      <c r="H131">
         <v>624</v>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t xml:space="preserve">311562918</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="J131" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
+      <c r="K131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6581,33 +7891,43 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rosenkildevej 20</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4640</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2581015</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F132">
+      <c r="H132">
         <v>369</v>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="I132" t="inlineStr">
         <is>
           <t xml:space="preserve">311567228</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="J132" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-10</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
+      <c r="K132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6631,33 +7951,43 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dannebrogsvej 1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4654</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t xml:space="preserve">8970979</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F133">
+      <c r="H133">
         <v>1672</v>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t xml:space="preserve">311585557</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="J133" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-16</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
+      <c r="K133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6681,39 +8011,49 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevej 4</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4653</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2585458</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F134">
+      <c r="H134">
         <v>1441</v>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t xml:space="preserve">311624091</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="J134" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-30</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
+      <c r="K134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J134"/>
+  <autoFilter ref="A1:L134"/>
 </worksheet>
 </file>
--- a/public/exports/29188475.xlsx
+++ b/public/exports/29188475.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 12A</t>
+          <t xml:space="preserve">Bavnestræde 28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100075735</t>
+          <t xml:space="preserve">7781615</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H2">
-        <v>851</v>
+        <v>1739</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 12B</t>
+          <t xml:space="preserve">Bækvej 3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100075735</t>
+          <t xml:space="preserve">2495761</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H3">
-        <v>463</v>
+        <v>1364</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 24</t>
+          <t xml:space="preserve">Bækvej 3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100075735</t>
+          <t xml:space="preserve">2495761</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H4">
-        <v>976</v>
+        <v>624</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækvej 3</t>
+          <t xml:space="preserve">Dannebrogsvej 3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4654</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2495761</t>
+          <t xml:space="preserve">719935, 8970979</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H5">
-        <v>1364</v>
+        <v>374</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækvej 3</t>
+          <t xml:space="preserve">Førslev Skolevej 9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2495761</t>
+          <t xml:space="preserve">2501202</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H6">
-        <v>624</v>
+        <v>1181</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Førslev Skolevej 9</t>
+          <t xml:space="preserve">Havnevej 10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4654</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2501202</t>
+          <t xml:space="preserve">719919, 2583548</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H7">
-        <v>1181</v>
+        <v>938</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevangen 8A</t>
+          <t xml:space="preserve">Jesper Olsens Vej 6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4683</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2586303</t>
+          <t xml:space="preserve">719857, 8970913</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H8">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 8A</t>
+          <t xml:space="preserve">Møllevangen 8A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4683</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">272693</t>
+          <t xml:space="preserve">2586303</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H9">
-        <v>1297</v>
+        <v>332</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 44</t>
+          <t xml:space="preserve">Søndergade 12A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">272693</t>
+          <t xml:space="preserve">100075735</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>574</v>
+        <v>851</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 10</t>
+          <t xml:space="preserve">Søndergade 12B</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">272693</t>
+          <t xml:space="preserve">100075735</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H11">
-        <v>1037</v>
+        <v>463</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 8E</t>
+          <t xml:space="preserve">Vesterled 24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">272693, 272694</t>
+          <t xml:space="preserve">100075735</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H12">
-        <v>1229</v>
+        <v>976</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 8D</t>
+          <t xml:space="preserve">Østervej 4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">272695</t>
+          <t xml:space="preserve">719853, 2580339</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>333</v>
+        <v>369</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grøndalsvej 8</t>
+          <t xml:space="preserve">Østervej 4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">273579, 273581</t>
+          <t xml:space="preserve">719853, 2580339</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H14">
-        <v>1765</v>
+        <v>516</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 5</t>
+          <t xml:space="preserve">Østervej 4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">273580</t>
+          <t xml:space="preserve">719853, 2580339</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H15">
-        <v>404</v>
+        <v>251</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,17 +931,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 13B</t>
+          <t xml:space="preserve">Dannebrogsvej 1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4654</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">278068, 278069</t>
+          <t xml:space="preserve">8970979</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -950,26 +950,26 @@
         </is>
       </c>
       <c r="H16">
-        <v>3518</v>
+        <v>1457</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311502367</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -991,45 +991,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervej 4</t>
+          <t xml:space="preserve">Dannebrogsvej 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4654</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">719853, 2580339</t>
+          <t xml:space="preserve">8970979</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H17">
-        <v>369</v>
+        <v>826</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311502367</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1051,45 +1051,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervej 4</t>
+          <t xml:space="preserve">Dannebrogsvej 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4654</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">719853, 2580339</t>
+          <t xml:space="preserve">8970979</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H18">
-        <v>516</v>
+        <v>1176</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311502367</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1111,45 +1111,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervej 4</t>
+          <t xml:space="preserve">Dannebrogsvej 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4654</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">719853, 2580339</t>
+          <t xml:space="preserve">8970979</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H19">
-        <v>251</v>
+        <v>1991</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311502367</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1171,45 +1171,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jesper Olsens Vej 6</t>
+          <t xml:space="preserve">Dannebrogsvej 1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4654</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">719857, 8970913</t>
+          <t xml:space="preserve">8970979</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H20">
-        <v>352</v>
+        <v>965</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311502367</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1231,45 +1231,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 10</t>
+          <t xml:space="preserve">Grøndalsvej 35</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4654</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">719919, 2583548</t>
+          <t xml:space="preserve">2494663</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>938</v>
+        <v>695</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311502366</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1291,45 +1291,45 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dannebrogsvej 3</t>
+          <t xml:space="preserve">Eskilstrupvej 3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4654</t>
+          <t xml:space="preserve">4683</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">719935, 8970979</t>
+          <t xml:space="preserve">1325124</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H22">
-        <v>374</v>
+        <v>1690</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311507976</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1351,45 +1351,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bavnestræde 28</t>
+          <t xml:space="preserve">Eskilstrupvej 3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4683</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7781615</t>
+          <t xml:space="preserve">1325124</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H23">
-        <v>1739</v>
+        <v>4602</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311507976</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grøndalsvej 35</t>
+          <t xml:space="preserve">Eskilstrupvej 3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4683</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494663</t>
+          <t xml:space="preserve">1325124</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H24">
-        <v>695</v>
+        <v>1918</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502366</t>
+          <t xml:space="preserve">311507976</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1471,35 +1471,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dannebrogsvej 1</t>
+          <t xml:space="preserve">Eskilstrupvej 7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4654</t>
+          <t xml:space="preserve">4683</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8970979</t>
+          <t xml:space="preserve">1325124</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H25">
-        <v>1457</v>
+        <v>2344</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502367</t>
+          <t xml:space="preserve">311507977</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1531,35 +1531,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dannebrogsvej 1</t>
+          <t xml:space="preserve">Gl Strandvej 12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4654</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">8970979</t>
+          <t xml:space="preserve">2580447</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H26">
-        <v>826</v>
+        <v>2421</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502367</t>
+          <t xml:space="preserve">311507982</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dannebrogsvej 1</t>
+          <t xml:space="preserve">Gl Strandvej 12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4654</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8970979</t>
+          <t xml:space="preserve">2580447</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,16 +1610,16 @@
         </is>
       </c>
       <c r="H27">
-        <v>1176</v>
+        <v>1417</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502367</t>
+          <t xml:space="preserve">311507984</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1651,35 +1651,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dannebrogsvej 1</t>
+          <t xml:space="preserve">Gl Strandvej 12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4654</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8970979</t>
+          <t xml:space="preserve">2580447</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H28">
-        <v>1991</v>
+        <v>1641</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502367</t>
+          <t xml:space="preserve">311507986</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1711,35 +1711,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dannebrogsvej 1</t>
+          <t xml:space="preserve">Gl Strandvej 12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4654</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">8970979</t>
+          <t xml:space="preserve">2580447</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H29">
-        <v>965</v>
+        <v>2100</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502367</t>
+          <t xml:space="preserve">311507980</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1771,30 +1771,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskilstrupvej 3</t>
+          <t xml:space="preserve">Gl Strandvej 12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4683</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325124</t>
+          <t xml:space="preserve">2580447</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H30">
-        <v>1690</v>
+        <v>676</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507976</t>
+          <t xml:space="preserve">311507981</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1831,35 +1831,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskilstrupvej 3</t>
+          <t xml:space="preserve">Bækvej 14</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4683</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325124</t>
+          <t xml:space="preserve">2493619</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H31">
-        <v>4602</v>
+        <v>1736</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507976</t>
+          <t xml:space="preserve">311513872</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1891,35 +1891,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskilstrupvej 7</t>
+          <t xml:space="preserve">Bækvej 14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4683</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325124</t>
+          <t xml:space="preserve">2493619</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H32">
-        <v>2344</v>
+        <v>1541</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507977</t>
+          <t xml:space="preserve">311513878</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskilstrupvej 3</t>
+          <t xml:space="preserve">Bækvej 14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4683</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325124</t>
+          <t xml:space="preserve">2493619</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H33">
-        <v>1918</v>
+        <v>9606</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507976</t>
+          <t xml:space="preserve">311513873</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2011,35 +2011,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Strandvej 12</t>
+          <t xml:space="preserve">Bækvej 14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580447</t>
+          <t xml:space="preserve">2493619</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H34">
-        <v>2421</v>
+        <v>1592</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507982</t>
+          <t xml:space="preserve">311513876</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2071,35 +2071,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Strandvej 12</t>
+          <t xml:space="preserve">Frederiksgade 9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580447</t>
+          <t xml:space="preserve">2491982</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H35">
-        <v>1417</v>
+        <v>977</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507984</t>
+          <t xml:space="preserve">311514701</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2131,35 +2131,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Strandvej 12</t>
+          <t xml:space="preserve">Frederiksgade 9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580447</t>
+          <t xml:space="preserve">2491982</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H36">
-        <v>1641</v>
+        <v>1464</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507986</t>
+          <t xml:space="preserve">311514701</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2191,35 +2191,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Strandvej 12</t>
+          <t xml:space="preserve">Frederiksgade 9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580447</t>
+          <t xml:space="preserve">2491982</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H37">
-        <v>2100</v>
+        <v>1140</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507980</t>
+          <t xml:space="preserve">311514701</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2251,35 +2251,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Strandvej 12</t>
+          <t xml:space="preserve">Frederiksgade 9</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580447</t>
+          <t xml:space="preserve">2491982</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H38">
-        <v>676</v>
+        <v>275</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507981</t>
+          <t xml:space="preserve">311514701</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-29</t>
+          <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækvej 14</t>
+          <t xml:space="preserve">Vibeeng Alle 2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493619</t>
+          <t xml:space="preserve">2496094</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2330,16 +2330,16 @@
         </is>
       </c>
       <c r="H39">
-        <v>1736</v>
+        <v>7175</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513872</t>
+          <t xml:space="preserve">311519033</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-20</t>
+          <t xml:space="preserve">2031-05-10</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2371,35 +2371,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækvej 14</t>
+          <t xml:space="preserve">Møllevej 6A</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4653</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493619</t>
+          <t xml:space="preserve">2585399</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H40">
-        <v>1541</v>
+        <v>1958</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513876</t>
+          <t xml:space="preserve">311520448</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-20</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækvej 14</t>
+          <t xml:space="preserve">Skolegade 39</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4653</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493619</t>
+          <t xml:space="preserve">2585399</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H41">
-        <v>9606</v>
+        <v>494</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513873</t>
+          <t xml:space="preserve">311520451</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-20</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækvej 14</t>
+          <t xml:space="preserve">Skolegade 39</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4653</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493619</t>
+          <t xml:space="preserve">2585399</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H42">
-        <v>1592</v>
+        <v>1627</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513876</t>
+          <t xml:space="preserve">311520451</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-20</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2551,35 +2551,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 9</t>
+          <t xml:space="preserve">Skolegade 39</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4653</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491982</t>
+          <t xml:space="preserve">2585399</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H43">
-        <v>977</v>
+        <v>1299</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514701</t>
+          <t xml:space="preserve">311520451</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-23</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,35 +2611,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 9</t>
+          <t xml:space="preserve">Skolegade 39</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4653</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491982</t>
+          <t xml:space="preserve">2585399</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H44">
-        <v>1464</v>
+        <v>1789</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514701</t>
+          <t xml:space="preserve">311520451</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-23</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,35 +2671,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 9</t>
+          <t xml:space="preserve">Skolegade 39</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4653</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491982</t>
+          <t xml:space="preserve">2585399</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H45">
-        <v>1140</v>
+        <v>1124</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514701</t>
+          <t xml:space="preserve">311520449</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-23</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,35 +2731,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 9</t>
+          <t xml:space="preserve">Industriparken 4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491982</t>
+          <t xml:space="preserve">2581322</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H46">
-        <v>275</v>
+        <v>647</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514701</t>
+          <t xml:space="preserve">311522394</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-23</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,35 +2791,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibeeng Alle 2</t>
+          <t xml:space="preserve">Industriparken 4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2496094</t>
+          <t xml:space="preserve">2581322</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H47">
-        <v>7175</v>
+        <v>486</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519033</t>
+          <t xml:space="preserve">311522394</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-10</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2851,35 +2851,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 39</t>
+          <t xml:space="preserve">Industriparken 4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4653</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585399</t>
+          <t xml:space="preserve">2581322</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H48">
-        <v>494</v>
+        <v>299</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520451</t>
+          <t xml:space="preserve">311522394</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,35 +2911,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 39</t>
+          <t xml:space="preserve">Sofiendalsvej 42A</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4653</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585399</t>
+          <t xml:space="preserve">2492828</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>1627</v>
+        <v>11412</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520451</t>
+          <t xml:space="preserve">311525403</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,35 +2971,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 39</t>
+          <t xml:space="preserve">Sofiendalsvej 42A</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4653</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585399</t>
+          <t xml:space="preserve">2492828</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H50">
-        <v>1299</v>
+        <v>764</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520451</t>
+          <t xml:space="preserve">311525403</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,35 +3031,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 6A</t>
+          <t xml:space="preserve">Terslev Skolevej 34A</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4653</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585399</t>
+          <t xml:space="preserve">2499032</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H51">
-        <v>1958</v>
+        <v>1058</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520448</t>
+          <t xml:space="preserve">311526266</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,35 +3091,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 39</t>
+          <t xml:space="preserve">Terslev Skolevej 34A</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4653</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585399</t>
+          <t xml:space="preserve">2499032</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H52">
-        <v>1789</v>
+        <v>745</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520451</t>
+          <t xml:space="preserve">311526270</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,35 +3151,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 39</t>
+          <t xml:space="preserve">Terslev Skolevej 34A</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4653</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585399</t>
+          <t xml:space="preserve">2499032</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H53">
-        <v>1124</v>
+        <v>285</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520449</t>
+          <t xml:space="preserve">311526268</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,35 +3211,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industriparken 4</t>
+          <t xml:space="preserve">Terslev Skolevej 34B</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2581322</t>
+          <t xml:space="preserve">2499032</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H54">
-        <v>647</v>
+        <v>296</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522394</t>
+          <t xml:space="preserve">311526267</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,35 +3271,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industriparken 4</t>
+          <t xml:space="preserve">Terslev Skolevej 36</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2581322</t>
+          <t xml:space="preserve">2499032</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H55">
-        <v>486</v>
+        <v>519</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522394</t>
+          <t xml:space="preserve">311526271</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,35 +3331,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industriparken 4</t>
+          <t xml:space="preserve">Tingvej 7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2581322</t>
+          <t xml:space="preserve">8141300</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H56">
-        <v>299</v>
+        <v>1564</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522394</t>
+          <t xml:space="preserve">311531956</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-06-29</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofiendalsvej 42A</t>
+          <t xml:space="preserve">Tingvej 7</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,25 +3401,25 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492828</t>
+          <t xml:space="preserve">8141300</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H57">
-        <v>11412</v>
+        <v>325</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525401</t>
+          <t xml:space="preserve">311531956</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-04</t>
+          <t xml:space="preserve">2031-06-29</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofiendalsvej 42A</t>
+          <t xml:space="preserve">Tingvej 7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,25 +3461,25 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492828</t>
+          <t xml:space="preserve">8141300</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H58">
-        <v>764</v>
+        <v>2032</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525401</t>
+          <t xml:space="preserve">311531956</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-04</t>
+          <t xml:space="preserve">2031-06-29</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terslev Skolevej 34A</t>
+          <t xml:space="preserve">Grøndalsvej 29A</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499032</t>
+          <t xml:space="preserve">2494640</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3530,16 +3530,16 @@
         </is>
       </c>
       <c r="H59">
-        <v>1058</v>
+        <v>675</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526266</t>
+          <t xml:space="preserve">311532866</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terslev Skolevej 34A</t>
+          <t xml:space="preserve">Grøndalsvej 31A</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499032</t>
+          <t xml:space="preserve">2494640</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="H60">
-        <v>745</v>
+        <v>675</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311532866</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terslev Skolevej 34B</t>
+          <t xml:space="preserve">Sofiendalsvej 42C</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,25 +3641,25 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499032</t>
+          <t xml:space="preserve">2492876</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>296</v>
+        <v>2115</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311533132</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,35 +3691,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terslev Skolevej 34A</t>
+          <t xml:space="preserve">Thujavej 19</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4683</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499032</t>
+          <t xml:space="preserve">9769474</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H62">
-        <v>285</v>
+        <v>746</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311533569</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,35 +3751,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terslev Skolevej 36</t>
+          <t xml:space="preserve">Thujavej 1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4683</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499032</t>
+          <t xml:space="preserve">9769474</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H63">
-        <v>519</v>
+        <v>679</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311533839</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-07-06</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,35 +3811,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 7</t>
+          <t xml:space="preserve">Thujavej 10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4683</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">8141300</t>
+          <t xml:space="preserve">9769474</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H64">
-        <v>1564</v>
+        <v>679</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531956</t>
+          <t xml:space="preserve">311533838</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-29</t>
+          <t xml:space="preserve">2031-07-06</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,35 +3871,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 7</t>
+          <t xml:space="preserve">Møllevej 68A</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4683</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8141300</t>
+          <t xml:space="preserve">2587199</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H65">
-        <v>325</v>
+        <v>2134</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531956</t>
+          <t xml:space="preserve">311534181</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-29</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 7</t>
+          <t xml:space="preserve">Søndergade 14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,25 +3941,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8141300</t>
+          <t xml:space="preserve">100080165</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H66">
-        <v>2032</v>
+        <v>2431</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531956</t>
+          <t xml:space="preserve">311534182</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-29</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grøndalsvej 29A</t>
+          <t xml:space="preserve">Bækvej 3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,25 +4001,25 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494640</t>
+          <t xml:space="preserve">2495761</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H67">
-        <v>675</v>
+        <v>394</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532866</t>
+          <t xml:space="preserve">311534554</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-01</t>
+          <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grøndalsvej 31A</t>
+          <t xml:space="preserve">Frederiksgade 10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4061,25 +4061,25 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494640</t>
+          <t xml:space="preserve">272693</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H68">
-        <v>675</v>
+        <v>1037</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532866</t>
+          <t xml:space="preserve">311564104</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-01</t>
+          <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofiendalsvej 42C</t>
+          <t xml:space="preserve">Frederiksgade 44</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,25 +4121,25 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492876</t>
+          <t xml:space="preserve">272693</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H69">
-        <v>2115</v>
+        <v>574</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533132</t>
+          <t xml:space="preserve">311564102</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,35 +4171,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thujavej 19</t>
+          <t xml:space="preserve">Frederiksgade 8A</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4683</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9769474</t>
+          <t xml:space="preserve">272693</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H70">
-        <v>746</v>
+        <v>1297</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533569</t>
+          <t xml:space="preserve">311564100</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,35 +4231,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thujavej 1</t>
+          <t xml:space="preserve">Frederiksgade 8D</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4683</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9769474</t>
+          <t xml:space="preserve">272695</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H71">
-        <v>679</v>
+        <v>333</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533839</t>
+          <t xml:space="preserve">311564101</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-06</t>
+          <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,35 +4291,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thujavej 10</t>
+          <t xml:space="preserve">Frederiksgade 8E</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4683</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9769474</t>
+          <t xml:space="preserve">272693, 272694</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H72">
-        <v>679</v>
+        <v>1229</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533838</t>
+          <t xml:space="preserve">311564103</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-06</t>
+          <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 14</t>
+          <t xml:space="preserve">Grøndalsvej 25A</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">100080165</t>
+          <t xml:space="preserve">8780170</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4370,16 +4370,16 @@
         </is>
       </c>
       <c r="H73">
-        <v>2431</v>
+        <v>660</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534182</t>
+          <t xml:space="preserve">311534676</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,35 +4411,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 68A</t>
+          <t xml:space="preserve">Grøndalsvej 27A</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4683</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2587199</t>
+          <t xml:space="preserve">8780170</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H74">
-        <v>2134</v>
+        <v>660</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534181</t>
+          <t xml:space="preserve">311534676</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækvej 3</t>
+          <t xml:space="preserve">Grøndalsvej 33A</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,20 +4481,20 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2495761</t>
+          <t xml:space="preserve">8780170</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H75">
-        <v>394</v>
+        <v>660</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534554</t>
+          <t xml:space="preserve">311534676</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heeringvej 3</t>
+          <t xml:space="preserve">Grøndalsvej 8</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,20 +4541,20 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579156</t>
+          <t xml:space="preserve">273579, 273581</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>936</v>
+        <v>1765</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534563</t>
+          <t xml:space="preserve">311534458</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4591,30 +4591,30 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusvej 4</t>
+          <t xml:space="preserve">Heeringvej 3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580442</t>
+          <t xml:space="preserve">2579156</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H77">
-        <v>1250</v>
+        <v>936</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534561</t>
+          <t xml:space="preserve">311534563</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grøndalsvej 25A</t>
+          <t xml:space="preserve">Rådhusvej 4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8780170</t>
+          <t xml:space="preserve">2580442</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4730,11 +4730,11 @@
         </is>
       </c>
       <c r="H79">
-        <v>660</v>
+        <v>1250</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534676</t>
+          <t xml:space="preserve">311534561</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grøndalsvej 27A</t>
+          <t xml:space="preserve">Jernbanegade 62</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,25 +4781,25 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8780170</t>
+          <t xml:space="preserve">2492101</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>660</v>
+        <v>4270</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534676</t>
+          <t xml:space="preserve">311554854</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-08</t>
+          <t xml:space="preserve">2031-07-19</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,35 +4831,35 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grøndalsvej 33A</t>
+          <t xml:space="preserve">Postvej 6</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4654</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8780170</t>
+          <t xml:space="preserve">8135543</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H81">
-        <v>660</v>
+        <v>1376</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534676</t>
+          <t xml:space="preserve">311536815</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-08</t>
+          <t xml:space="preserve">2031-07-19</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 62</t>
+          <t xml:space="preserve">Bavnestræde 42</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,25 +4901,25 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492101</t>
+          <t xml:space="preserve">2579174</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H82">
-        <v>4270</v>
+        <v>351</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554854</t>
+          <t xml:space="preserve">311537312</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-19</t>
+          <t xml:space="preserve">2031-07-22</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,35 +4951,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postvej 6</t>
+          <t xml:space="preserve">Bavnestræde 46</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4654</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8135543</t>
+          <t xml:space="preserve">2579174</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H83">
-        <v>1376</v>
+        <v>1088</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311536815</t>
+          <t xml:space="preserve">311537312</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-19</t>
+          <t xml:space="preserve">2031-07-22</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5071,35 +5071,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bavnestræde 46</t>
+          <t xml:space="preserve">Præstøvej 86</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579174</t>
+          <t xml:space="preserve">2581990</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H85">
-        <v>1088</v>
+        <v>4123</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311537312</t>
+          <t xml:space="preserve">311538599</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-22</t>
+          <t xml:space="preserve">2031-08-02</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bavnestræde 42</t>
+          <t xml:space="preserve">Søndergade 12</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5141,25 +5141,25 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579174</t>
+          <t xml:space="preserve">2494366</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H86">
-        <v>351</v>
+        <v>1300</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311537312</t>
+          <t xml:space="preserve">311539272</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-22</t>
+          <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,35 +5191,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstøvej 86</t>
+          <t xml:space="preserve">Søndergade 12C</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2581990</t>
+          <t xml:space="preserve">2494366</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H87">
-        <v>4123</v>
+        <v>416</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538599</t>
+          <t xml:space="preserve">311539269</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-02</t>
+          <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 12</t>
+          <t xml:space="preserve">Søndergade 12G</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5326,15 +5326,15 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H89">
-        <v>1300</v>
+        <v>1387</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539272</t>
+          <t xml:space="preserve">311539175</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 12C</t>
+          <t xml:space="preserve">Bavnestræde 28</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494366</t>
+          <t xml:space="preserve">7781615</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H90">
-        <v>416</v>
+        <v>1119</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539269</t>
+          <t xml:space="preserve">311541554</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-05</t>
+          <t xml:space="preserve">2031-08-18</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 12G</t>
+          <t xml:space="preserve">Bavnestræde 28</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,25 +5441,25 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2494366</t>
+          <t xml:space="preserve">7781615</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H91">
-        <v>1387</v>
+        <v>633</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539175</t>
+          <t xml:space="preserve">311541554</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-05</t>
+          <t xml:space="preserve">2031-08-18</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bavnestræde 28</t>
+          <t xml:space="preserve">Bavnestræde 36</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5501,20 +5501,20 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7781615</t>
+          <t xml:space="preserve">7781616</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H92">
-        <v>1119</v>
+        <v>2900</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541554</t>
+          <t xml:space="preserve">311541553</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bavnestræde 28</t>
+          <t xml:space="preserve">Sygehusvej 5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5561,25 +5561,25 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">7781615</t>
+          <t xml:space="preserve">273580</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H93">
-        <v>633</v>
+        <v>404</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541554</t>
+          <t xml:space="preserve">311542625</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-18</t>
+          <t xml:space="preserve">2031-08-23</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,35 +5611,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bavnestræde 36</t>
+          <t xml:space="preserve">Gl Strandvej 2</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7781616</t>
+          <t xml:space="preserve">2580360</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H94">
-        <v>2900</v>
+        <v>581</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541553</t>
+          <t xml:space="preserve">311543100</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-18</t>
+          <t xml:space="preserve">2031-08-25</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,30 +5671,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndermarken 1</t>
+          <t xml:space="preserve">Gl Strandvej 2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2496094</t>
+          <t xml:space="preserve">2580362</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H95">
-        <v>698</v>
+        <v>379</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543099</t>
+          <t xml:space="preserve">311543101</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5731,30 +5731,30 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Strandvej 2</t>
+          <t xml:space="preserve">Søndermarken 1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580360</t>
+          <t xml:space="preserve">2496094</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H96">
-        <v>581</v>
+        <v>698</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543100</t>
+          <t xml:space="preserve">311543099</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5791,35 +5791,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Strandvej 2</t>
+          <t xml:space="preserve">Skolegade 42</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4653</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580362</t>
+          <t xml:space="preserve">2585634</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H97">
-        <v>379</v>
+        <v>833</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543101</t>
+          <t xml:space="preserve">311543427</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-25</t>
+          <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,17 +5851,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 42</t>
+          <t xml:space="preserve">Kirkevej 18A</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4653</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585634</t>
+          <t xml:space="preserve">2499489</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5870,16 +5870,16 @@
         </is>
       </c>
       <c r="H98">
-        <v>833</v>
+        <v>2089</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543427</t>
+          <t xml:space="preserve">311544512</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-26</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 18A</t>
+          <t xml:space="preserve">Kirkevej 18C</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5926,15 +5926,15 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H99">
-        <v>2089</v>
+        <v>253</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544512</t>
+          <t xml:space="preserve">311544514</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5971,30 +5971,30 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 18C</t>
+          <t xml:space="preserve">Ny Strandvej 3A</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499489</t>
+          <t xml:space="preserve">9827159</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H100">
-        <v>253</v>
+        <v>707</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544514</t>
+          <t xml:space="preserve">311544498</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6031,17 +6031,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Strandvej 3A</t>
+          <t xml:space="preserve">Maglemosevej 9</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827159</t>
+          <t xml:space="preserve">2493974</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6050,16 +6050,16 @@
         </is>
       </c>
       <c r="H101">
-        <v>707</v>
+        <v>368</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544498</t>
+          <t xml:space="preserve">311544973</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-09-01</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglemosevej 9</t>
+          <t xml:space="preserve">Terslev Skolevej 30B</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6101,20 +6101,20 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493974</t>
+          <t xml:space="preserve">2499035</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H102">
-        <v>368</v>
+        <v>642</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544973</t>
+          <t xml:space="preserve">311544971</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terslev Skolevej 30B</t>
+          <t xml:space="preserve">Drosselvej 1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4683</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499035</t>
+          <t xml:space="preserve">8975253</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H103">
-        <v>642</v>
+        <v>585</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544971</t>
+          <t xml:space="preserve">311545558</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-01</t>
+          <t xml:space="preserve">2031-09-03</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,17 +6211,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvej 1</t>
+          <t xml:space="preserve">Præstøvej 3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4683</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8975253</t>
+          <t xml:space="preserve">8295199</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6230,16 +6230,16 @@
         </is>
       </c>
       <c r="H104">
-        <v>585</v>
+        <v>715</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545558</t>
+          <t xml:space="preserve">311545939</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-03</t>
+          <t xml:space="preserve">2031-09-06</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,17 +6271,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstøvej 3</t>
+          <t xml:space="preserve">Lindeparken 33</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8295199</t>
+          <t xml:space="preserve">7941733</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="H105">
-        <v>715</v>
+        <v>538</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545939</t>
+          <t xml:space="preserve">311546917</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-06</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindeparken 33</t>
+          <t xml:space="preserve">Stadionvej 8</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">7941733</t>
+          <t xml:space="preserve">9945281</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6410,16 +6410,16 @@
         </is>
       </c>
       <c r="H107">
-        <v>538</v>
+        <v>300</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546917</t>
+          <t xml:space="preserve">311548105</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 8</t>
+          <t xml:space="preserve">Præstevænget 23</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,25 +6461,25 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">9945281</t>
+          <t xml:space="preserve">2491982</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H108">
-        <v>300</v>
+        <v>365</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548105</t>
+          <t xml:space="preserve">311548233</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-14</t>
+          <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstevænget 23</t>
+          <t xml:space="preserve">Sofiendalsvej 4</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6521,20 +6521,20 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491982</t>
+          <t xml:space="preserve">2493365</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H109">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548233</t>
+          <t xml:space="preserve">311548273</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofiendalsvej 4</t>
+          <t xml:space="preserve">Stadionvej 10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493365</t>
+          <t xml:space="preserve">9340703</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6590,11 +6590,11 @@
         </is>
       </c>
       <c r="H110">
-        <v>374</v>
+        <v>496</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548273</t>
+          <t xml:space="preserve">311548275</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6691,17 +6691,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 10</t>
+          <t xml:space="preserve">Vindbyholtvej 30B</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9340703</t>
+          <t xml:space="preserve">2588105</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6710,16 +6710,16 @@
         </is>
       </c>
       <c r="H112">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548275</t>
+          <t xml:space="preserve">311548921</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-15</t>
+          <t xml:space="preserve">2031-09-17</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,17 +6751,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindbyholtvej 30B</t>
+          <t xml:space="preserve">Frøgårdsvej 21</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4690</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2588105</t>
+          <t xml:space="preserve">2492872</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6770,16 +6770,16 @@
         </is>
       </c>
       <c r="H113">
-        <v>535</v>
+        <v>352</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548921</t>
+          <t xml:space="preserve">311550934</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-17</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H114">
@@ -6886,11 +6886,11 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H115">
-        <v>352</v>
+        <v>406</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frøgårdsvej 21</t>
+          <t xml:space="preserve">Førslev Bygade 16A</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6941,25 +6941,25 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492872</t>
+          <t xml:space="preserve">8127744</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H116">
-        <v>406</v>
+        <v>697</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550934</t>
+          <t xml:space="preserve">311551270</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-09-28</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Førslev Bygade 16A</t>
+          <t xml:space="preserve">Lindhardsvej 5</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7001,25 +7001,25 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8127744</t>
+          <t xml:space="preserve">2579410</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H117">
-        <v>697</v>
+        <v>2332</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551270</t>
+          <t xml:space="preserve">311557163</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-28</t>
+          <t xml:space="preserve">2031-10-25</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,35 +7051,35 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindhardsvej 5</t>
+          <t xml:space="preserve">Ny Strandvej 1C</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579410</t>
+          <t xml:space="preserve">100328633</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H118">
-        <v>2332</v>
+        <v>283</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557163</t>
+          <t xml:space="preserve">311557973</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-25</t>
+          <t xml:space="preserve">2031-10-27</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Strandvej 1C</t>
+          <t xml:space="preserve">Hertelsvej 18</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">100328633</t>
+          <t xml:space="preserve">9978417</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7190,16 +7190,16 @@
         </is>
       </c>
       <c r="H120">
-        <v>283</v>
+        <v>1430</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557973</t>
+          <t xml:space="preserve">311560035</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-27</t>
+          <t xml:space="preserve">2031-11-05</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hertelsvej 18</t>
+          <t xml:space="preserve">Hertelsvej 16</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7241,25 +7241,25 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9978417</t>
+          <t xml:space="preserve">2580961</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H121">
-        <v>1430</v>
+        <v>288</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560035</t>
+          <t xml:space="preserve">311562931</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-05</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hertelsvej 16</t>
+          <t xml:space="preserve">Præstøvej 78A</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,20 +7301,20 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580961</t>
+          <t xml:space="preserve">2580963</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H122">
-        <v>288</v>
+        <v>2118</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562929</t>
+          <t xml:space="preserve">311562912</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7366,15 +7366,15 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H123">
-        <v>2118</v>
+        <v>1875</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562912</t>
+          <t xml:space="preserve">311562920</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7426,15 +7426,15 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H124">
-        <v>1875</v>
+        <v>2727</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311562913</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstøvej 78B</t>
+          <t xml:space="preserve">Præstøvej 78A</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7486,15 +7486,15 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H125">
-        <v>1266</v>
+        <v>2961</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311562914</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7546,15 +7546,15 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H126">
-        <v>2727</v>
+        <v>2156</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562913</t>
+          <t xml:space="preserve">311562915</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7606,15 +7606,15 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H127">
-        <v>2961</v>
+        <v>516</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311562916</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7666,15 +7666,15 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H128">
-        <v>2156</v>
+        <v>890</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562915</t>
+          <t xml:space="preserve">311562926</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7726,15 +7726,15 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H129">
-        <v>516</v>
+        <v>624</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562916</t>
+          <t xml:space="preserve">311562919</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstøvej 78A</t>
+          <t xml:space="preserve">Præstøvej 78B</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7786,15 +7786,15 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H130">
-        <v>890</v>
+        <v>1266</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311562924</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstøvej 78A</t>
+          <t xml:space="preserve">Rosenkildevej 20</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7841,25 +7841,25 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580963</t>
+          <t xml:space="preserve">2581015</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H131">
-        <v>624</v>
+        <v>369</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311567228</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2031-12-10</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,35 +7891,35 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 20</t>
+          <t xml:space="preserve">Dannebrogsvej 1</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">4640</t>
+          <t xml:space="preserve">4654</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2581015</t>
+          <t xml:space="preserve">8970979</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H132">
-        <v>369</v>
+        <v>1672</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567228</t>
+          <t xml:space="preserve">311585557</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-10</t>
+          <t xml:space="preserve">2032-03-16</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,35 +7951,35 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dannebrogsvej 1</t>
+          <t xml:space="preserve">Møllevej 4</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4654</t>
+          <t xml:space="preserve">4653</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">8970979</t>
+          <t xml:space="preserve">2585458</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H133">
-        <v>1672</v>
+        <v>1441</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585557</t>
+          <t xml:space="preserve">311624091</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-16</t>
+          <t xml:space="preserve">2032-08-30</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 4</t>
+          <t xml:space="preserve">Lindevej 13B</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4653</t>
+          <t xml:space="preserve">4640</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2585458</t>
+          <t xml:space="preserve">278068, 278069</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8030,16 +8030,16 @@
         </is>
       </c>
       <c r="H134">
-        <v>1441</v>
+        <v>3518</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624091</t>
+          <t xml:space="preserve">311682804</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-30</t>
+          <t xml:space="preserve">2033-05-24</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">

--- a/public/exports/29188475.xlsx
+++ b/public/exports/29188475.xlsx
@@ -1914,7 +1914,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513878</t>
+          <t xml:space="preserve">311513876</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525403</t>
+          <t xml:space="preserve">311525402</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525403</t>
+          <t xml:space="preserve">311525402</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526266</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526270</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526268</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526267</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526271</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544512</t>
+          <t xml:space="preserve">311544511</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562931</t>
+          <t xml:space="preserve">311562929</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562912</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562920</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562913</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562914</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562926</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562919</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562924</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">

--- a/public/exports/29188475.xlsx
+++ b/public/exports/29188475.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L134"/>
+  <dimension ref="A1:M134"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-29</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1854,20 +2004,25 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513872</t>
+          <t xml:space="preserve">311513876</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1974,20 +2134,25 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513873</t>
+          <t xml:space="preserve">311513876</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-10</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2934,20 +3174,25 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525402</t>
+          <t xml:space="preserve">311525401</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2994,20 +3239,25 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525402</t>
+          <t xml:space="preserve">311525401</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3054,20 +3304,25 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311526266</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3114,20 +3369,25 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311526272</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3174,20 +3434,25 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311526272</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3234,20 +3499,25 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311526267</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3294,20 +3564,25 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311526272</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-29</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-29</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-29</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-06</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-06</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-08</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-19</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-19</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-22</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-22</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-22</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-02</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-18</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-18</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-18</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-23</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-25</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-25</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-25</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5874,20 +6359,25 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544511</t>
+          <t xml:space="preserve">311544512</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5934,20 +6424,25 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544514</t>
+          <t xml:space="preserve">311544517</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-01</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-01</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-03</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-06</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-17</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6954,20 +7529,25 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551270</t>
+          <t xml:space="preserve">311551273</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-28</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-25</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-27</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-27</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-05</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7254,20 +7854,25 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562929</t>
+          <t xml:space="preserve">311562931</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7314,20 +7919,25 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311562912</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7374,20 +7984,25 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7434,20 +8049,25 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311562913</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7494,20 +8114,25 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311562914</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7554,20 +8179,25 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562915</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7614,20 +8244,25 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562916</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7674,20 +8309,25 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7734,20 +8374,25 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7794,20 +8439,25 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-10</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-16</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-30</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,21 +8704,26 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-24</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L134"/>
+  <autoFilter ref="A1:M134"/>
 </worksheet>
 </file>
--- a/public/exports/29188475.xlsx
+++ b/public/exports/29188475.xlsx
@@ -2004,12 +2004,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513876</t>
+          <t xml:space="preserve">311513872</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513876</t>
+          <t xml:space="preserve">311513873</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3369,12 +3369,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526272</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526272</t>
+          <t xml:space="preserve">311526268</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526272</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544512</t>
+          <t xml:space="preserve">311544511</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544517</t>
+          <t xml:space="preserve">311544511</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551273</t>
+          <t xml:space="preserve">311551269</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562931</t>
+          <t xml:space="preserve">311562929</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562915</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562916</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
